--- a/Restoration Mountaine Forest - ANR 50% Enrichment (with_NTFP).xlsx
+++ b/Restoration Mountaine Forest - ANR 50% Enrichment (with_NTFP).xlsx
@@ -2293,7 +2293,7 @@
         <v>Coffea arabica</v>
       </c>
       <c r="FL3">
-        <v>80</v>
+        <v>4.64</v>
       </c>
       <c r="FM3">
         <v>1</v>
